--- a/files/港岛-半山区西部-宝峰.xlsx
+++ b/files/港岛-半山区西部-宝峰.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -969,7 +969,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1918,7 +1918,7 @@
           <t>A | 6702呎 (4+房)
 $42000万
 $62,668/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
           <t>A | 4049呎 (4+房)
 $27000万
 $66,683/呎
-(23年-10月-03日)</t>
+(23年-10月-04日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1974,7 +1974,7 @@
           <t>B | 3692呎 (3房)
 $20300万
 $54,984/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
           <t>A | 4049呎 (4+房)
 $18244万
 $45,057/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -1997,7 +1997,7 @@
           <t>B | 3699呎 (4+房)
 $16263万
 $43,966/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
           <t>A | 4049呎 (3房)
 $19000万
 $46,925/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2020,7 +2020,7 @@
           <t>B | 3699呎 (4+房)
 $16159万
 $43,684/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
           <t>A | 4049呎 (4+房)
 $18644万
 $46,045/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -2043,7 +2043,7 @@
           <t>B | 3699呎 (4+房)
 $16500万
 $44,607/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
           <t>A | 4049呎 (4+房)
 $17000万
 $41,986/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -2066,7 +2066,7 @@
           <t>B | 3699呎 (4+房)
 $15100万
 $40,822/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
           <t>A | 4049呎 (4+房)
 $18000万
 $44,455/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -2089,7 +2089,7 @@
           <t>B | 3700呎 (4+房)
 $15100万
 $40,811/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
           <t>A | 3861呎 (3房)
 $17479万
 $45,270/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>

--- a/files/港岛-半山区西部-宝峰.xlsx
+++ b/files/港岛-半山区西部-宝峰.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,6 +121,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
@@ -201,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,7 +272,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -824,7 +833,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -834,12 +843,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -849,12 +858,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -864,7 +873,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1866,27 +1875,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1932,9 +1941,9 @@
       <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 6799呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -1945,7 +1954,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 7263呎 (4+房)
 -

--- a/files/港岛-半山区西部-宝峰.xlsx
+++ b/files/港岛-半山区西部-宝峰.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,12 +121,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
@@ -207,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -272,10 +266,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -833,7 +824,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -843,12 +834,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -858,12 +849,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -873,7 +864,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1866,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -1895,7 +1886,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1941,9 +1932,9 @@
       <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 6799呎 (4+房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -1954,7 +1945,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 7263呎 (4+房)
 -

--- a/files/港岛-半山区西部-宝峰.xlsx
+++ b/files/港岛-半山区西部-宝峰.xlsx
@@ -824,23 +824,19 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>399000000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>58685</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -1876,7 +1872,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -1886,7 +1882,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1925,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 6799呎 (4+房)
--
--
-(待售)</t>
+$39900万
+$58,685/呎
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
